--- a/data/warn-scraper/cache/ky/archive.xlsx
+++ b/data/warn-scraper/cache/ky/archive.xlsx
@@ -35769,17 +35769,43 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF0C1C9366252B4C838708442C71C5AA" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0e058ae9440022103accfd660e84addb">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6834f8c0c0eabdc6c42b2f987c760c09">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF0C1C9366252B4C838708442C71C5AA" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="623745db76138c409ead4834ced54ea8">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="62511544-38af-49c2-8996-37c0f6a636fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c1a1049adbb8cd97fc988c6af4986c32" ns2:_="">
+    <xsd:import namespace="62511544-38af-49c2-8996-37c0f6a636fd"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
-              <xsd:all/>
+              <xsd:all>
+                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
+              </xsd:all>
             </xsd:complexType>
           </xsd:element>
         </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="62511544-38af-49c2-8996-37c0f6a636fd" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
@@ -35898,7 +35924,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58F7E577-3CEF-4190-9612-CB66D6A5E833}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26F34954-AEAB-48F5-AF9D-C426A8F76B09}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
